--- a/tests/fixtures/kb/past_answers/past_answer_2023.xlsx
+++ b/tests/fixtures/kb/past_answers/past_answer_2023.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>セキュリティポリシーに基づき実施。年次レビューを実施。</t>
+          <t>情報セキュリティポリシー v2.8に基づき運用中。2023年3月にレビュー実施。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>クラウド関連の条項が未整備のため次年度改定予定</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -478,17 +478,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>一部実施している</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>主要システムには適用済み。レガシーシステムは対応中。</t>
+          <t>リスクアセスメント手順書(RA-PROC-2023)に基づき年1回の評価を実施。2023年11月完了。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>定量的リスク評価の手法を検討中</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -505,22 +505,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>実施している</t>
+          <t>一部実施している</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>規程に基づき運用中。四半期ごとにレビュー。</t>
+          <t>主要システムはIAM基盤で管理しているが、部門サーバー約15台は個別管理のまま。棚卸は半期ごと。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>統合ID管理基盤の全社展開を2024年度に計画</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -532,22 +532,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>計画中</t>
+          <t>一部実施している</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>次年度に導入予定。ベンダー選定中。</t>
+          <t>インターネットバンキングおよびVPN接続にMFA（SMS認証）を適用済み。社内システムはID/パスワード認証が主。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>全重要システムへのMFA展開を2024年度に計画</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -564,12 +564,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>全システムに適用済み。自動化ツールで管理。</t>
+          <t>ファイアウォール(FortiGate 600E)によるゾーン分離を実施。IDS(Snort)でネットワーク監視を実施中。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>次世代ファイアウォールへの更改を2024年度に予定</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -586,22 +586,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>実施している</t>
+          <t>一部実施している</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>セキュリティポリシーに基づき実施。年次レビューを実施。</t>
+          <t>重要システム（勘定系、インターネットバンキング）のログは統合管理。その他はサーバー個別保管。ログ保存期間は5年。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>統合SIEM導入プロジェクトを2024年度に開始予定</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -613,17 +613,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>一部実施している</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>主要システムには適用済み。レガシーシステムは対応中。</t>
+          <t>CSIRT体制を2022年度に構築。インシデント対応手順書(IRP-2023-v1)に基づき年2回の訓練を実施。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>ランサムウェア対応手順の整備が課題</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -640,22 +640,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>実施している</t>
+          <t>一部実施している</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>規程に基づき運用中。四半期ごとにレビュー。</t>
+          <t>四半期ごとの脆弱性スキャン(Nessus)を外部委託で実施。CVSS 9.0以上は即時対応、7.0以上は1ヶ月以内に対応。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>継続的スキャン体制への移行を検討中</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -667,22 +667,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>計画中</t>
+          <t>一部実施している</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>次年度に導入予定。ベンダー選定中。</t>
+          <t>勘定系データベースおよび個人情報DBはAES-256暗号化適用済み。ファイルサーバー上のデータは未暗号化。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>全データベースへの暗号化拡大を計画中。HSM導入も検討。</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -694,22 +694,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>実施している</t>
+          <t>一部実施している</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>全システムに適用済み。自動化ツールで管理。</t>
+          <t>外部通信はTLS 1.2以上を適用済み。社内一部システムでTLS 1.0が残存。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>2024年度末までに全面TLS 1.2以上に移行予定</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -726,17 +726,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>セキュリティポリシーに基づき実施。年次レビューを実施。</t>
+          <t>日次フルバックアップを実施。テープ媒体での遠隔地保管（月次搬送）。リストアテストは年1回。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>RTO/RPOの見直しとクラウドバックアップの検討を開始</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>主要システムには適用済み。レガシーシステムは対応中。</t>
+          <t>BCP基本計画書(BCP-2023)を策定済み。DR訓練は年1回実施。ただしDRサイトは単一拠点（大阪）のみ。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>クラウドDR環境の構築を2024年度に計画</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>規程に基づき運用中。四半期ごとにレビュー。</t>
+          <t>データセンターはISO 27001認証取得施設。入退室はICカード管理。監視カメラ24時間稼働。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>生体認証の追加導入を2024年度に計画</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -802,22 +802,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>計画中</t>
+          <t>一部実施している</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>次年度に導入予定。ベンダー選定中。</t>
+          <t>主要委託先（上位10社）に対し年次セキュリティ評価を実施。その他はチェックリストベースの自己評価。</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>全委託先への直接監査を段階的に拡大予定</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -834,17 +834,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>全システムに適用済み。自動化ツールで管理。</t>
+          <t>全従業員向けeラーニング（年1回必須）を実施。受講率97.8%。標的型メール訓練を年2回実施、開封率8.2%。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>役職別専門研修の拡充を計画</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -861,17 +861,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>セキュリティポリシーに基づき実施。年次レビューを実施。</t>
+          <t>全端末にウイルス対策ソフト(Symantec Endpoint Protection)を導入。パターンファイル自動更新を適用。</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>EDR導入を2024年度に計画（CrowdStrike検討中）</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -883,17 +883,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>一部実施している</t>
+          <t>実施している</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>主要システムには適用済み。レガシーシステムは対応中。</t>
+          <t>変更管理プロセス(CHG-PROC-v2)に基づき運用。変更諮問委員会（月1回開催）で承認。RedmineでチケットI管理。</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>ServiceNowへの移行を検討中</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -910,22 +910,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>実施している</t>
+          <t>一部実施している</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>規程に基づき運用中。四半期ごとにレビュー。</t>
+          <t>セキュアコーディングガイドライン(SCG-2022)を策定。リリース前にSAST(SonarQube)を実施。DASTは外部委託で年1回。</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>CI/CDパイプラインへのセキュリティツール組込みを2024年度に計画</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>次年度に導入予定。ベンダー選定中。</t>
+          <t>クラウド利用ガイドライン(CLD-GL-2023)を策定。AWS環境のセキュリティ設定はマニュアルレビューで対応。</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>CSPM導入およびクラウドセキュリティ管理基準の策定を2024年度に計画</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -969,17 +969,287 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>全システムに適用済み。自動化ツールで管理。</t>
+          <t>個人情報保護管理規程(PII-MGT-v3)に基づき運用。個人情報台帳による管理を実施。</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2023年度対応</t>
+          <t>DLPツールの導入を2024年度に計画。PIAプロセスは未整備。</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>一部実施している</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>特権IDの利用申請・承認フローを運用中。ログ取得は実施しているが、操作録画は未対応。パスワード変更は手動。</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>特権ID管理ツール（PAM）の導入を2024年度に計画</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>一部実施している</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>主要API連携にはOAuth 2.0を適用。一部レガシーシステムではAPIキー方式が残存。API利用状況の監視は手動集計。</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>API管理基盤の導入を2024年度に検討開始</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>一部実施している</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>会社貸与端末にMDM(MobileIron)を導入。BYODは原則禁止だが、一部部門で例外運用あり。</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MDMの更改（Intune移行）とBYODポリシーの明確化を計画</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>内部監査部門による年次IT監査を実施。2023年度報告書(IA-RPT-2023-009)で軽微な指摘2件あり（是正済み）。</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SOC2 Type II取得に向けた準備を開始</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>実施している</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>コンプライアンス委員会（四半期開催）で法令改正対応を管理。FISC安全対策基準への準拠を年次で確認。</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GRCプラットフォーム導入による効率化を検討中</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>一部実施している</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>メールフィルタリング(Barracuda)を導入。SPF設定済み。DKIM対応済み。</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DMARC導入を2024年度に予定。添付ファイル自動暗号化を検討中。</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>一部実施している</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ハードウェア資産はIT資産管理台帳（Excel）で管理。ソフトウェアはLANSCOPEで自動検出。棚卸は半期ごと。</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>統合資産管理ツールの導入を計画中</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>計画中</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>パッチ適用率（月次集計：93.2%）とインシデント件数を管理。報告は四半期ごと。</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>KPIの体系的な整備とダッシュボード構築を2024年度に計画</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>計画中</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ゼロトラストに関する調査・検討を開始。外部コンサルタントによるアセスメントを2023年12月に実施。</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ゼロトラスト移行ロードマップを2024年度に策定予定</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>一部実施している</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>年1回のサイバー演習（机上演習形式）を実施。2023年度は金融ISAC主催の情報共有会に参加。</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TLPT実施を2024年度に計画。Red Team演習の導入も検討。</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>
